--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486817_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486817_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. THIAW</t>
+          <t>J. MEJIA ECHEVERRY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3727</v>
+        <v>4.8362</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4607</v>
+        <v>5.6033</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.7672</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2377</v>
+        <v>2.9403</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7803</v>
+        <v>1.1861</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5426</v>
+        <v>1.7542</v>
       </c>
       <c r="J2" t="n">
-        <v>2.094</v>
+        <v>4.6177</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8498</v>
+        <v>1.8076</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2442</v>
+        <v>2.81</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8563</v>
+        <v>-1.6774</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-1.0558</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1931</v>
+        <v>2.1239</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1239</v>
+        <v>3.0892</v>
       </c>
       <c r="S2" t="n">
-        <v>7.3973</v>
+        <v>1.6135</v>
       </c>
       <c r="T2" t="n">
-        <v>6.0119</v>
+        <v>1.3372</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3854</v>
+        <v>0.2763</v>
       </c>
       <c r="V2" t="n">
+        <v>-1.8415</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.6138</v>
+      </c>
+      <c r="X2" t="n">
         <v>-2.4554</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.2856</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-2.741</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MEJIA ECHEVERRY</t>
+          <t>L. BUENO CASTILLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8225</v>
+        <v>4.6714</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3413</v>
+        <v>4.3003</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5188</v>
+        <v>0.371</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9403</v>
+        <v>3.5821</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1861</v>
+        <v>3.6702</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7542</v>
+        <v>-0.0882</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6177</v>
+        <v>4.7145</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8076</v>
+        <v>4.0158</v>
       </c>
       <c r="L3" t="n">
-        <v>2.81</v>
+        <v>0.6986</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6774</v>
+        <v>-1.1324</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6215000000000001</v>
+        <v>-0.3456</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0558</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1239</v>
+        <v>0.7723</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0892</v>
+        <v>2.7031</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5998</v>
+        <v>0.9308</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0752</v>
+        <v>0.9028</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5246</v>
+        <v>0.028</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.8415</v>
+        <v>-0.6138</v>
       </c>
       <c r="W3" t="n">
         <v>0.6138</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.4554</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. BUENO CASTILLO</t>
+          <t>L. BULASHVILI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9997</v>
+        <v>3.9188</v>
       </c>
       <c r="E4" t="n">
-        <v>3.728</v>
+        <v>4.1204</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2717</v>
+        <v>-0.2016</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5821</v>
+        <v>0.471</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6702</v>
+        <v>0.0142</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0882</v>
+        <v>0.4568</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7145</v>
+        <v>2.0724</v>
       </c>
       <c r="K4" t="n">
-        <v>4.0158</v>
+        <v>0.4287</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6986</v>
+        <v>1.6437</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1324</v>
+        <v>-1.6014</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3456</v>
+        <v>-0.4145</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-1.1869</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7723</v>
+        <v>2.1239</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7031</v>
+        <v>3.0892</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2592</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3305</v>
+        <v>0.5581</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0713</v>
+        <v>0.1521</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6138</v>
+        <v>0.6138</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6138</v>
+        <v>2.4554</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2277</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2052</v>
+        <v>3.6603</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9144</v>
+        <v>4.1212</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.4609</v>
       </c>
       <c r="G5" t="n">
         <v>1.1063</v>
@@ -844,13 +844,13 @@
         <v>2.7031</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.276</v>
+        <v>0.1791</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3857</v>
+        <v>0.5925</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6617</v>
+        <v>-0.4134</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3282</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. BULASHVILI</t>
+          <t>M. MELERO JAREÑO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8902</v>
+        <v>2.4432</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5139</v>
+        <v>3.0372</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6237</v>
+        <v>-0.5939</v>
       </c>
       <c r="G6" t="n">
-        <v>0.471</v>
+        <v>-0.9774</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0142</v>
+        <v>-1.2622</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4568</v>
+        <v>0.2848</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0724</v>
+        <v>1.5336</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4287</v>
+        <v>-0.5032</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6437</v>
+        <v>2.0369</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6014</v>
+        <v>-2.511</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4145</v>
+        <v>-0.759</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1869</v>
+        <v>-1.7521</v>
       </c>
       <c r="P6" t="n">
+        <v>0.1931</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-1.9308</v>
+      </c>
+      <c r="R6" t="n">
         <v>2.1239</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-0.9654</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3.0892</v>
-      </c>
       <c r="S6" t="n">
-        <v>-1.3185</v>
+        <v>0.7722</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0485</v>
+        <v>0.9789</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.27</v>
+        <v>-0.2068</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6138</v>
+        <v>2.4554</v>
       </c>
       <c r="W6" t="n">
         <v>2.4554</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. MELERO JAREÑO</t>
+          <t>M. THIAW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6985</v>
+        <v>2.0921</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4166</v>
+        <v>2.9995</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7181</v>
+        <v>-0.9074</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9774</v>
+        <v>1.2377</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2622</v>
+        <v>1.7803</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2848</v>
+        <v>-0.5426</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5336</v>
+        <v>2.094</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5032</v>
+        <v>1.8498</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0369</v>
+        <v>0.2442</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.511</v>
+        <v>-0.8563</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.759</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7521</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="P7" t="n">
         <v>0.1931</v>
@@ -1000,28 +1000,28 @@
         <v>2.1239</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0275</v>
+        <v>3.1167</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3584</v>
+        <v>2.5507</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3309</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>2.4554</v>
+        <v>-2.4554</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4554</v>
+        <v>0.2856</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. BAILLO HERNÁNDEZ</t>
+          <t>E. QUIJADA GARCÍA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4309</v>
+        <v>1.1569</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1631</v>
+        <v>1.2953</v>
       </c>
       <c r="F8" t="n">
-        <v>0.594</v>
+        <v>-0.1384</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1759</v>
+        <v>-0.3876</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8828</v>
+        <v>0.4691</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2931</v>
+        <v>-0.8567</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0927</v>
+        <v>1.1714</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6067</v>
+        <v>0.6762</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.486</v>
+        <v>0.4952</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0832</v>
+        <v>-1.559</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2761</v>
+        <v>-0.2071</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8071</v>
+        <v>-1.3519</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1585</v>
+        <v>1.3515</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1585</v>
+        <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8771</v>
+        <v>0.1929</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3584</v>
+        <v>0.1239</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5187</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. QUIJADA GARCÍA</t>
+          <t>B. BAILLO HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4122</v>
+        <v>0.2296</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6747</v>
+        <v>-0.3148</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2626</v>
+        <v>0.5443</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3876</v>
+        <v>-2.1759</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4691</v>
+        <v>-0.8828</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8567</v>
+        <v>-1.2931</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1714</v>
+        <v>-1.0927</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6762</v>
+        <v>-0.6067</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4952</v>
+        <v>-0.486</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.559</v>
+        <v>-1.0832</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2071</v>
+        <v>-0.2761</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3519</v>
+        <v>-0.8071</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3515</v>
+        <v>1.1585</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3515</v>
+        <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5518</v>
+        <v>0.6758</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4966</v>
+        <v>0.2067</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0551</v>
+        <v>0.469</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1544</v>
+        <v>0.1792</v>
       </c>
       <c r="E10" t="n">
         <v>0.0207</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1337</v>
+        <v>0.1585</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2483</v>
@@ -1234,13 +1234,13 @@
         <v>0.3862</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9629</v>
+        <v>-1.8884</v>
       </c>
       <c r="E11" t="n">
         <v>-1.8135</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1494</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7864</v>
@@ -1312,13 +1312,13 @@
         <v>0.5792</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4469</v>
+        <v>-0.3724</v>
       </c>
       <c r="T11" t="n">
         <v>-0.2207</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2261</v>
+        <v>-0.1516</v>
       </c>
       <c r="V11" t="n">
         <v>0.6565</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>21.0234</v>
+        <v>21.2993</v>
       </c>
       <c r="E12" t="n">
-        <v>23.0937</v>
+        <v>23.3696</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.070400000000001</v>
+        <v>-2.0705</v>
       </c>
       <c r="G12" t="n">
-        <v>3.761799999999998</v>
+        <v>3.7618</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7956</v>
+        <v>3.795599999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.03379999999999972</v>
+        <v>-0.03380000000000016</v>
       </c>
       <c r="J12" t="n">
         <v>17.2187</v>
@@ -1390,28 +1390,28 @@
         <v>19.3078</v>
       </c>
       <c r="S12" t="n">
-        <v>7.5843</v>
+        <v>7.860199999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>6.7543</v>
+        <v>7.0301</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8302</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9420000000000001</v>
+        <v>-0.9419999999999996</v>
       </c>
       <c r="W12" t="n">
         <v>7.8094</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.751500000000002</v>
+        <v>-8.7515</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. SOTO RODRIGUEZ</t>
+          <t>M. VILLANUEVA CUBELO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5647</v>
+        <v>1.484</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0103</v>
+        <v>4.5749</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4455</v>
+        <v>-3.091</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1548</v>
+        <v>2.7319</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2897</v>
+        <v>1.206</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1349</v>
+        <v>1.5259</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0458</v>
+        <v>3.175</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5319</v>
+        <v>1.1381</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.486</v>
+        <v>2.0369</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.891</v>
+        <v>-0.4431</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2422</v>
+        <v>0.0679</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6489</v>
+        <v>-0.511</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.7031</v>
+        <v>0.1931</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R13" t="n">
         <v>1.1585</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3294</v>
+        <v>-1.441</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1855</v>
+        <v>-0.09</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1439</v>
+        <v>-1.351</v>
       </c>
       <c r="V13" t="n">
-        <v>2.7836</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.6404</v>
+        <v>2.4554</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8568</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. VILLANUEVA CUBELO</t>
+          <t>I. SOTO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2316</v>
+        <v>0.456</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4715</v>
+        <v>1.976</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.24</v>
+        <v>-1.52</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7319</v>
+        <v>0.1548</v>
       </c>
       <c r="H14" t="n">
-        <v>1.206</v>
+        <v>1.2897</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5259</v>
+        <v>-1.1349</v>
       </c>
       <c r="J14" t="n">
-        <v>3.175</v>
+        <v>2.0458</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1381</v>
+        <v>2.5319</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0369</v>
+        <v>-0.486</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4431</v>
+        <v>-1.891</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0679</v>
+        <v>-1.2422</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.511</v>
+        <v>-0.6489</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1931</v>
+        <v>-2.7031</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R14" t="n">
         <v>1.1585</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6934</v>
+        <v>0.2207</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1934</v>
+        <v>0.1513</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5</v>
+        <v>0.0694</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>2.7836</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4554</v>
+        <v>3.6404</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.4554</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.547</v>
+        <v>0.4477</v>
       </c>
       <c r="E15" t="n">
         <v>0.07530000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4716</v>
+        <v>0.3723</v>
       </c>
       <c r="G15" t="n">
         <v>1.4682</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0441</v>
+        <v>-0.0552</v>
       </c>
       <c r="T15" t="n">
         <v>-0.2207</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2649</v>
+        <v>0.1655</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.631</v>
+        <v>0.031</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5906</v>
+        <v>2.0043</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2216</v>
+        <v>-1.9733</v>
       </c>
       <c r="G16" t="n">
         <v>0.8443000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>1.1585</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.9307</v>
+        <v>-1.2687</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4415</v>
+        <v>-0.0278</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4892</v>
+        <v>-1.2409</v>
       </c>
       <c r="V16" t="n">
         <v>1.2277</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.1344</v>
+        <v>-1.7993</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0989</v>
+        <v>2.4092</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.2334</v>
+        <v>-4.2085</v>
       </c>
       <c r="G17" t="n">
         <v>2.1105</v>
@@ -1780,13 +1780,13 @@
         <v>1.7377</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8588</v>
+        <v>-1.5237</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.359</v>
+        <v>-0.0487</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.4998</v>
+        <v>-1.475</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2277</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5821</v>
+        <v>-2.756</v>
       </c>
       <c r="E18" t="n">
         <v>-0.1975</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3846</v>
+        <v>-2.5585</v>
       </c>
       <c r="G18" t="n">
         <v>-1.4821</v>
@@ -1858,13 +1858,13 @@
         <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2465</v>
+        <v>-1.4203</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0279</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2186</v>
+        <v>-1.3924</v>
       </c>
       <c r="V18" t="n">
         <v>1.8842</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.8106</v>
+        <v>-3.7154</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1189</v>
+        <v>-2.2223</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6917</v>
+        <v>-1.4931</v>
       </c>
       <c r="G19" t="n">
         <v>-1.8353</v>
@@ -1936,13 +1936,13 @@
         <v>0.5792</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0332</v>
+        <v>0.062</v>
       </c>
       <c r="T19" t="n">
-        <v>0.248</v>
+        <v>0.1446</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2813</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5559</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0414</v>
+        <v>-3.8883</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4199</v>
+        <v>-0.3164</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.6215</v>
+        <v>-3.5719</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7932</v>
@@ -2014,13 +2014,13 @@
         <v>0.3862</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7116</v>
+        <v>-0.5585</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3311</v>
+        <v>-0.2277</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3805</v>
+        <v>-0.3308</v>
       </c>
       <c r="V20" t="n">
         <v>0.0426</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0114</v>
+        <v>-4.9866</v>
       </c>
       <c r="E21" t="n">
         <v>-3.2484</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.763</v>
+        <v>-1.7382</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6141</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2042</v>
+        <v>-0.1793</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2759</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0717</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2277</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.1557</v>
+        <v>-6.2965</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1917</v>
+        <v>-2.9848</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.964</v>
+        <v>-3.3116</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3468</v>
@@ -2170,13 +2170,13 @@
         <v>1.3515</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2795</v>
+        <v>-1.4203</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4142</v>
+        <v>-0.2073</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8653999999999999</v>
+        <v>-1.213</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9847</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-21.0233</v>
+        <v>-21.0234</v>
       </c>
       <c r="E23" t="n">
-        <v>2.070200000000001</v>
+        <v>2.0703</v>
       </c>
       <c r="F23" t="n">
-        <v>-23.0937</v>
+        <v>-23.0938</v>
       </c>
       <c r="G23" t="n">
         <v>-3.7618</v>
@@ -2248,13 +2248,13 @@
         <v>8.688600000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.5844</v>
+        <v>-7.5843</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8302</v>
+        <v>-0.8301000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.7543</v>
+        <v>-6.754200000000001</v>
       </c>
       <c r="V23" t="n">
         <v>0.9421000000000005</v>
